--- a/research/traditional_assets/database/data/pakistan/pakistan_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_publishing_newspapers.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.193</v>
+        <v>-0.183</v>
       </c>
       <c r="G2">
-        <v>-0.386034255599473</v>
+        <v>-0.03289473684210526</v>
       </c>
       <c r="H2">
-        <v>-0.386034255599473</v>
+        <v>-0.03289473684210526</v>
       </c>
       <c r="I2">
-        <v>-0.5994729907773386</v>
+        <v>-0.3042763157894737</v>
       </c>
       <c r="J2">
-        <v>-0.5994729907773386</v>
+        <v>-0.3042763157894737</v>
       </c>
       <c r="K2">
-        <v>-0.639</v>
+        <v>-0.446</v>
       </c>
       <c r="L2">
-        <v>-0.8418972332015811</v>
+        <v>-0.7335526315789473</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,73 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="V2">
-        <v>0.005855855855855855</v>
+        <v>0.00326797385620915</v>
       </c>
       <c r="W2">
-        <v>0.1224137931034483</v>
+        <v>0.07824561403508772</v>
       </c>
       <c r="X2">
-        <v>0.2193282462534194</v>
+        <v>0.395525991311333</v>
       </c>
       <c r="Y2">
-        <v>-0.09691445314997114</v>
-      </c>
-      <c r="Z2">
-        <v>-0.2380056444026341</v>
-      </c>
-      <c r="AA2">
-        <v>0.1426779554719348</v>
+        <v>-0.3172803772762453</v>
       </c>
       <c r="AB2">
-        <v>0.1239544411883876</v>
-      </c>
-      <c r="AC2">
-        <v>0.01872351428354724</v>
+        <v>0.2142514136391233</v>
       </c>
       <c r="AD2">
-        <v>3.38</v>
+        <v>2.52</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>3.38</v>
+        <v>2.52</v>
       </c>
       <c r="AG2">
-        <v>3.367</v>
+        <v>2.515</v>
       </c>
       <c r="AH2">
-        <v>0.6035714285714285</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="AI2">
-        <v>-1.456896551724138</v>
+        <v>-1.150684931506849</v>
       </c>
       <c r="AJ2">
-        <v>0.6026490066225166</v>
+        <v>0.6217552533992584</v>
       </c>
       <c r="AK2">
-        <v>-1.44320617231033</v>
+        <v>-1.145785876993166</v>
       </c>
       <c r="AL2">
-        <v>0.323</v>
+        <v>0.339</v>
       </c>
       <c r="AM2">
-        <v>0.323</v>
+        <v>0.339</v>
       </c>
       <c r="AN2">
-        <v>-13.05019305019305</v>
+        <v>-48.46153846153847</v>
       </c>
       <c r="AO2">
-        <v>-1.408668730650155</v>
+        <v>-0.5457227138643067</v>
       </c>
       <c r="AP2">
-        <v>-13</v>
+        <v>-48.36538461538462</v>
       </c>
       <c r="AQ2">
-        <v>-1.408668730650155</v>
+        <v>-0.5457227138643067</v>
       </c>
     </row>
     <row r="3">
@@ -716,25 +707,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.193</v>
+        <v>-0.183</v>
       </c>
       <c r="G3">
-        <v>-0.386034255599473</v>
+        <v>-0.03289473684210526</v>
       </c>
       <c r="H3">
-        <v>-0.386034255599473</v>
+        <v>-0.03289473684210526</v>
       </c>
       <c r="I3">
-        <v>-0.5994729907773386</v>
+        <v>-0.3042763157894737</v>
       </c>
       <c r="J3">
-        <v>-0.5994729907773386</v>
+        <v>-0.3042763157894737</v>
       </c>
       <c r="K3">
-        <v>-0.639</v>
+        <v>-0.446</v>
       </c>
       <c r="L3">
-        <v>-0.8418972332015811</v>
+        <v>-0.7335526315789473</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -758,73 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.013</v>
+        <v>0.005</v>
       </c>
       <c r="V3">
-        <v>0.005855855855855855</v>
+        <v>0.00326797385620915</v>
       </c>
       <c r="W3">
-        <v>0.1224137931034483</v>
+        <v>0.07824561403508772</v>
       </c>
       <c r="X3">
-        <v>0.2193282462534194</v>
+        <v>0.395525991311333</v>
       </c>
       <c r="Y3">
-        <v>-0.09691445314997114</v>
-      </c>
-      <c r="Z3">
-        <v>-0.2380056444026341</v>
-      </c>
-      <c r="AA3">
-        <v>0.1426779554719348</v>
+        <v>-0.3172803772762453</v>
       </c>
       <c r="AB3">
-        <v>0.1239544411883876</v>
-      </c>
-      <c r="AC3">
-        <v>0.01872351428354724</v>
+        <v>0.2142514136391233</v>
       </c>
       <c r="AD3">
-        <v>3.38</v>
+        <v>2.52</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>3.38</v>
+        <v>2.52</v>
       </c>
       <c r="AG3">
-        <v>3.367</v>
+        <v>2.515</v>
       </c>
       <c r="AH3">
-        <v>0.6035714285714285</v>
+        <v>0.6222222222222222</v>
       </c>
       <c r="AI3">
-        <v>-1.456896551724138</v>
+        <v>-1.150684931506849</v>
       </c>
       <c r="AJ3">
-        <v>0.6026490066225166</v>
+        <v>0.6217552533992584</v>
       </c>
       <c r="AK3">
-        <v>-1.44320617231033</v>
+        <v>-1.145785876993166</v>
       </c>
       <c r="AL3">
-        <v>0.323</v>
+        <v>0.339</v>
       </c>
       <c r="AM3">
-        <v>0.323</v>
+        <v>0.339</v>
       </c>
       <c r="AN3">
-        <v>-13.05019305019305</v>
+        <v>-48.46153846153847</v>
       </c>
       <c r="AO3">
-        <v>-1.408668730650155</v>
+        <v>-0.5457227138643067</v>
       </c>
       <c r="AP3">
-        <v>-13</v>
+        <v>-48.36538461538462</v>
       </c>
       <c r="AQ3">
-        <v>-1.408668730650155</v>
+        <v>-0.5457227138643067</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_publishing_newspapers.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_publishing_newspapers.xlsx
@@ -588,25 +588,25 @@
         </is>
       </c>
       <c r="D2">
-        <v>-0.183</v>
+        <v>-0.208</v>
       </c>
       <c r="G2">
-        <v>-0.03289473684210526</v>
+        <v>-0.4117647058823529</v>
       </c>
       <c r="H2">
-        <v>-0.03289473684210526</v>
+        <v>-0.4117647058823529</v>
       </c>
       <c r="I2">
-        <v>-0.3042763157894737</v>
+        <v>-0.6229946524064172</v>
       </c>
       <c r="J2">
-        <v>-0.3042763157894737</v>
+        <v>-0.6229946524064172</v>
       </c>
       <c r="K2">
-        <v>-0.446</v>
+        <v>-0.358</v>
       </c>
       <c r="L2">
-        <v>-0.7335526315789473</v>
+        <v>-0.9572192513368983</v>
       </c>
       <c r="M2">
         <v>0</v>
@@ -630,64 +630,64 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="V2">
-        <v>0.00326797385620915</v>
+        <v>0.0007874015748031496</v>
       </c>
       <c r="W2">
-        <v>0.07824561403508772</v>
+        <v>0.07600849256900212</v>
       </c>
       <c r="X2">
-        <v>0.395525991311333</v>
+        <v>0.3925509730944385</v>
       </c>
       <c r="Y2">
-        <v>-0.3172803772762453</v>
+        <v>-0.3165424805254364</v>
       </c>
       <c r="AB2">
-        <v>0.2142514136391233</v>
+        <v>0.2382719096051809</v>
       </c>
       <c r="AD2">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG2">
-        <v>2.515</v>
+        <v>1.569</v>
       </c>
       <c r="AH2">
-        <v>0.6222222222222222</v>
+        <v>0.5528169014084507</v>
       </c>
       <c r="AI2">
-        <v>-1.150684931506849</v>
+        <v>-0.7235023041474655</v>
       </c>
       <c r="AJ2">
-        <v>0.6217552533992584</v>
+        <v>0.5526593871081367</v>
       </c>
       <c r="AK2">
-        <v>-1.145785876993166</v>
+        <v>-0.7227084292952556</v>
       </c>
       <c r="AL2">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="AM2">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="AN2">
-        <v>-48.46153846153847</v>
+        <v>-10.60810810810811</v>
       </c>
       <c r="AO2">
-        <v>-0.5457227138643067</v>
+        <v>-0.6619318181818182</v>
       </c>
       <c r="AP2">
-        <v>-48.36538461538462</v>
+        <v>-10.60135135135135</v>
       </c>
       <c r="AQ2">
-        <v>-0.5457227138643067</v>
+        <v>-0.6619318181818182</v>
       </c>
     </row>
     <row r="3">
@@ -707,25 +707,25 @@
         </is>
       </c>
       <c r="D3">
-        <v>-0.183</v>
+        <v>-0.208</v>
       </c>
       <c r="G3">
-        <v>-0.03289473684210526</v>
+        <v>-0.4117647058823529</v>
       </c>
       <c r="H3">
-        <v>-0.03289473684210526</v>
+        <v>-0.4117647058823529</v>
       </c>
       <c r="I3">
-        <v>-0.3042763157894737</v>
+        <v>-0.6229946524064172</v>
       </c>
       <c r="J3">
-        <v>-0.3042763157894737</v>
+        <v>-0.6229946524064172</v>
       </c>
       <c r="K3">
-        <v>-0.446</v>
+        <v>-0.358</v>
       </c>
       <c r="L3">
-        <v>-0.7335526315789473</v>
+        <v>-0.9572192513368983</v>
       </c>
       <c r="M3">
         <v>-0</v>
@@ -749,64 +749,64 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>0.005</v>
+        <v>0.001</v>
       </c>
       <c r="V3">
-        <v>0.00326797385620915</v>
+        <v>0.0007874015748031496</v>
       </c>
       <c r="W3">
-        <v>0.07824561403508772</v>
+        <v>0.07600849256900212</v>
       </c>
       <c r="X3">
-        <v>0.395525991311333</v>
+        <v>0.3925509730944385</v>
       </c>
       <c r="Y3">
-        <v>-0.3172803772762453</v>
+        <v>-0.3165424805254364</v>
       </c>
       <c r="AB3">
-        <v>0.2142514136391233</v>
+        <v>0.2382719096051809</v>
       </c>
       <c r="AD3">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>2.52</v>
+        <v>1.57</v>
       </c>
       <c r="AG3">
-        <v>2.515</v>
+        <v>1.569</v>
       </c>
       <c r="AH3">
-        <v>0.6222222222222222</v>
+        <v>0.5528169014084507</v>
       </c>
       <c r="AI3">
-        <v>-1.150684931506849</v>
+        <v>-0.7235023041474655</v>
       </c>
       <c r="AJ3">
-        <v>0.6217552533992584</v>
+        <v>0.5526593871081367</v>
       </c>
       <c r="AK3">
-        <v>-1.145785876993166</v>
+        <v>-0.7227084292952556</v>
       </c>
       <c r="AL3">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="AM3">
-        <v>0.339</v>
+        <v>0.352</v>
       </c>
       <c r="AN3">
-        <v>-48.46153846153847</v>
+        <v>-10.60810810810811</v>
       </c>
       <c r="AO3">
-        <v>-0.5457227138643067</v>
+        <v>-0.6619318181818182</v>
       </c>
       <c r="AP3">
-        <v>-48.36538461538462</v>
+        <v>-10.60135135135135</v>
       </c>
       <c r="AQ3">
-        <v>-0.5457227138643067</v>
+        <v>-0.6619318181818182</v>
       </c>
     </row>
   </sheetData>
